--- a/ODIN-Model/assumptions.xlsx
+++ b/ODIN-Model/assumptions.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assumptions'!$A$4:$G$29</definedName>
@@ -1510,7 +1511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1704,7 +1705,7 @@
       <c r="D12" s="19" t="inlineStr"/>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>1/298.257223563. Used only for the drag height.</t>
+          <t>1/298.257223563. Used for the drag height, the ground station positions and the ground track.</t>
         </is>
       </c>
     </row>
@@ -1775,14 +1776,18 @@
         </is>
       </c>
       <c r="C16" s="28" t="n">
-        <v>800</v>
+        <v>625</v>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
           <t>km</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr"/>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Osculating at the start, orbit-mean altitude about 620.2 km.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
@@ -1796,14 +1801,18 @@
         </is>
       </c>
       <c r="C17" s="28" t="n">
-        <v>98.6</v>
+        <v>97.5</v>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>deg</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr"/>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>GNC value. Sun synchronous at 625 km would be 97.851 (ssoInclination), so the LTAN drifts about -64 min per year.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
@@ -1817,14 +1826,18 @@
         </is>
       </c>
       <c r="C18" s="28" t="n">
-        <v>0</v>
+        <v>83.9718</v>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
           <t>deg</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr"/>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>LTAN 06:00 at cfg.epoch, mean Sun as in tradeLighting.m. GNC gave 115, which is LTAN 06:00 on 16 Oct 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
@@ -1888,23 +1901,23 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>Switches</t>
+          <t>Constellation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>J2 acceleration</t>
+          <t>Number of orbit planes</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>cfg.use.J2</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="b">
-        <v>1</v>
+          <t>cfg.const.nPlanes</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>3</v>
       </c>
       <c r="D23" s="19" t="inlineStr"/>
       <c r="E23" s="19" t="inlineStr"/>
@@ -1912,304 +1925,427 @@
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>Sun direction and Earth shadow history</t>
+          <t>Satellites per plane</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>cfg.use.eclipse</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="b">
-        <v>1</v>
+          <t>cfg.const.nPerPlane</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>3</v>
       </c>
       <c r="D24" s="19" t="inlineStr"/>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>Needed by solarFlux.m and eclipseTimes.m.</t>
-        </is>
-      </c>
+      <c r="E24" s="19" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>Atmospheric drag in the Jacchia 1977 atmosphere</t>
+          <t>RAAN step between planes</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>cfg.use.drag</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="19" t="inlineStr"/>
+          <t>cfg.const.dRaan</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>Off by default so existing results are unchanged; set true to include drag.</t>
+          <t>Plane k has RAAN cfg.raan0 + (k-1)*dRaan.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>Solar radiation pressure</t>
+          <t>Along-track step between satellites in a plane</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>cfg.use.srp</t>
-        </is>
-      </c>
-      <c r="C26" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="19" t="inlineStr"/>
+          <t>cfg.const.dU</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>120</v>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>Not implemented.</t>
+          <t>Taken in time as dU/360 of the nodal period, so a plane shares one trajectory.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>Shadow geometry</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>cfg.eclipse.model</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>conical</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr"/>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>'conical' or 'cylindrical'.</t>
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Switches</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Spacecraft and drag</t>
-        </is>
-      </c>
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>J2 acceleration</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>cfg.use.J2</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="19" t="inlineStr"/>
+      <c r="E28" s="19" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>Spacecraft mass</t>
+          <t>Sun direction and Earth shadow history</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>cfg.drag.mass</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+          <t>cfg.use.eclipse</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="19" t="inlineStr"/>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Needed by solarFlux.m and eclipseTimes.m.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>Mean cross-sectional area normal to the flow</t>
+          <t>Atmospheric drag in the Jacchia 1977 atmosphere</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>cfg.drag.area</t>
-        </is>
-      </c>
-      <c r="C30" s="28" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>cfg.use.drag</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="19" t="inlineStr"/>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Off by default so existing results are unchanged; set true to include drag.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>Drag coefficient</t>
+          <t>Solar radiation pressure</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>cfg.drag.Cd</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="n">
-        <v>2.2</v>
+          <t>cfg.use.srp</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="b">
+        <v>0</v>
       </c>
       <c r="D31" s="19" t="inlineStr"/>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Not implemented.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>10.7 cm solar flux, daily and 81-day mean</t>
+          <t>Shadow geometry</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>cfg.drag.F107</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="n">
-        <v>150</v>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>sfu</t>
-        </is>
-      </c>
+          <t>cfg.eclipse.model</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>conical</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr"/>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>Held constant for the whole run. CelesTrak forecast mean for Sep 2026 to Sep 2027 is about 107.</t>
+          <t>'conical' or 'cylindrical'.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>Solver</t>
+          <t>Spacecraft and drag</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>ode45 relative error tolerance</t>
+          <t>Spacecraft mass</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>cfg.ode.relTol</t>
-        </is>
-      </c>
-      <c r="C34" s="29" t="n">
-        <v>1e-11</v>
-      </c>
-      <c r="D34" s="19" t="inlineStr"/>
-      <c r="E34" s="19" t="inlineStr"/>
+          <t>cfg.drag.mass</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>ode45 absolute error tolerance</t>
+          <t>Mean cross-sectional area normal to the flow</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>cfg.ode.absTol</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="n">
-        <v>1e-11</v>
-      </c>
-      <c r="D35" s="19" t="inlineStr"/>
-      <c r="E35" s="19" t="inlineStr"/>
+          <t>cfg.drag.area</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>Spacing of the uniform output time grid</t>
+          <t>Drag coefficient</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>cfg.ode.dtOut</t>
+          <t>cfg.drag.Cd</t>
         </is>
       </c>
       <c r="C36" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="D36" s="19" t="inlineStr"/>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>Sets the sampling only, not the integration accuracy.</t>
+          <t>Placeholder</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>Derived</t>
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>10.7 cm solar flux, daily and 81-day mean</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>cfg.drag.F107</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>sfu</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>Held constant for the whole run. CelesTrak forecast mean for Sep 2026 to Sep 2027 is about 107.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>Ballistic coefficient m/(Cd A)</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="n"/>
-      <c r="C38" s="30">
-        <f>C29/(C31*C30)</f>
-        <v/>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>kg/m²</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>Derived</t>
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
+          <t>Solar panel front-face area</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>cfg.power.panelArea</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>0.1977</v>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>Total physical area per satellite, passed to arrayPower by main_demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>Solver</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>ode45 relative error tolerance</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>cfg.ode.relTol</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="n">
+        <v>1e-11</v>
+      </c>
+      <c r="D41" s="19" t="inlineStr"/>
+      <c r="E41" s="19" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>ode45 absolute error tolerance</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>cfg.ode.absTol</t>
+        </is>
+      </c>
+      <c r="C42" s="29" t="n">
+        <v>1e-11</v>
+      </c>
+      <c r="D42" s="19" t="inlineStr"/>
+      <c r="E42" s="19" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>Spacing of the uniform output time grid</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>cfg.ode.dtOut</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Sets the sampling only, not the integration accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>Ballistic coefficient m/(Cd A)</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="30">
+        <f>C34/(C36*C35)</f>
+        <v/>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>kg/m²</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
           <t>Exospheric temperature, J77 eq. 20 at Kp = 0</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="30">
-        <f>5.48*C32^0.8+101.8*C32^0.4</f>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="30">
+        <f>5.48*C37^0.8+101.8*C37^0.4</f>
         <v/>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
+      <c r="E46" s="19" t="inlineStr">
         <is>
           <t>Derived</t>
         </is>
@@ -2222,6 +2358,128 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Ground stations read by stations.m</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Latitude [deg]</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Longitude [deg, east positive]</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Altitude [m]</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Mask angle [deg]</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>KSAT Svalbard</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="n">
+        <v>78.229</v>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>From the team ground station list, which gives no altitude or mask, so 0 m and 10 deg are assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>NASA McMurdo</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="n">
+        <v>-77.85</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>166.63</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>From the team ground station list, which gives no altitude or mask, so 0 m and 10 deg are assumed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3119,7 +3377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
